--- a/DataTables/Datas/animationstate.xlsx
+++ b/DataTables/Datas/animationstate.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -1019,6 +1019,481 @@
         <v>0</v>
       </c>
     </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>5001</v>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>think1</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>talk</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>5003</v>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>idle1</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>6001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>think1</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>6002</v>
+      </c>
+      <c r="C37" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>talk</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>6003</v>
+      </c>
+      <c r="C38" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>talk2</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>6004</v>
+      </c>
+      <c r="C39" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>idle1</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C40" t="n">
+        <v>7</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>7001</v>
+      </c>
+      <c r="C41" t="n">
+        <v>7</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>7002</v>
+      </c>
+      <c r="C42" t="n">
+        <v>7</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>attack2</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>7003</v>
+      </c>
+      <c r="C43" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>die</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>7004</v>
+      </c>
+      <c r="C44" t="n">
+        <v>7</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C45" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C46" t="n">
+        <v>9</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>9001</v>
+      </c>
+      <c r="C47" t="n">
+        <v>9</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>idle1</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C48" t="n">
+        <v>10</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>idle1</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>10001</v>
+      </c>
+      <c r="C49" t="n">
+        <v>10</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>idle2</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>10002</v>
+      </c>
+      <c r="C50" t="n">
+        <v>10</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>idle3</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C51" t="n">
+        <v>11</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>idle1</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>11001</v>
+      </c>
+      <c r="C52" t="n">
+        <v>11</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>idle2</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>11002</v>
+      </c>
+      <c r="C53" t="n">
+        <v>11</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>idle3</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C54" t="n">
+        <v>12</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>12001</v>
+      </c>
+      <c r="C55" t="n">
+        <v>12</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DataTables/Datas/animationstate.xlsx
+++ b/DataTables/Datas/animationstate.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -1494,6 +1494,177 @@
         <v>0</v>
       </c>
     </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>2003</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>2004</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>2005</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>die</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>3003</v>
+      </c>
+      <c r="C60" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>3004</v>
+      </c>
+      <c r="C61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>3005</v>
+      </c>
+      <c r="C62" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>3006</v>
+      </c>
+      <c r="C63" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>hurt</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>3007</v>
+      </c>
+      <c r="C64" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>die</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
